--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127074321</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127074070</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127073751</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127074243</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127074706</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127073807</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127073629</v>
+        <v>127074790</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>91773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,38 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786926</v>
+        <v>786929</v>
       </c>
       <c r="R8" t="n">
-        <v>7146477</v>
+        <v>7146554</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1428,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127074790</v>
+        <v>127073629</v>
       </c>
       <c r="B9" t="n">
-        <v>91699</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,34 +1435,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786929</v>
+        <v>786926</v>
       </c>
       <c r="R9" t="n">
-        <v>7146554</v>
+        <v>7146477</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1535,32 +1535,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127074190</v>
+        <v>127075032</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>91269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786967</v>
+        <v>786917</v>
       </c>
       <c r="R10" t="n">
-        <v>7146521</v>
+        <v>7146541</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,32 +1642,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127075032</v>
+        <v>127074190</v>
       </c>
       <c r="B11" t="n">
-        <v>91195</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>786917</v>
+        <v>786967</v>
       </c>
       <c r="R11" t="n">
-        <v>7146541</v>
+        <v>7146521</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>58516</v>
+        <v>91319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R14" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>91245</v>
+        <v>58516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R15" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,45 +2235,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127704</v>
+        <v>127127724</v>
       </c>
       <c r="B17" t="n">
-        <v>91603</v>
+        <v>57670</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786885</v>
+        <v>786865</v>
       </c>
       <c r="R17" t="n">
-        <v>7146464</v>
+        <v>7146487</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2314,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,7 +2348,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2429,53 +2442,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127724</v>
+        <v>127127704</v>
       </c>
       <c r="B19" t="n">
-        <v>57670</v>
+        <v>91677</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100048</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786865</v>
+        <v>786885</v>
       </c>
       <c r="R19" t="n">
-        <v>7146487</v>
+        <v>7146464</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,11 +2513,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2542,7 +2542,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127127705</v>
+        <v>127127703</v>
       </c>
       <c r="B21" t="n">
-        <v>91603</v>
+        <v>91677</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>786856</v>
+        <v>786966</v>
       </c>
       <c r="R21" t="n">
-        <v>7146424</v>
+        <v>7146509</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127127703</v>
+        <v>127127705</v>
       </c>
       <c r="B22" t="n">
-        <v>91603</v>
+        <v>91677</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>786966</v>
+        <v>786856</v>
       </c>
       <c r="R22" t="n">
-        <v>7146509</v>
+        <v>7146424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2830,42 +2830,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127716</v>
+        <v>127127725</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>91691</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1505</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2873,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786907</v>
+        <v>786938</v>
       </c>
       <c r="R23" t="n">
-        <v>7146524</v>
+        <v>7146481</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2911,12 +2906,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2938,7 +2939,7 @@
         <v>127127701</v>
       </c>
       <c r="B24" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,37 +3033,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127725</v>
+        <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>91617</v>
+        <v>57654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1505</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3070,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786938</v>
+        <v>786907</v>
       </c>
       <c r="R25" t="n">
-        <v>7146481</v>
+        <v>7146524</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,18 +3114,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>127127822</v>
       </c>
       <c r="B26" t="n">
-        <v>92059</v>
+        <v>92133</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B28" t="n">
-        <v>91263</v>
+        <v>91319</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R28" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B29" t="n">
-        <v>91245</v>
+        <v>91337</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R29" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,7 +3538,7 @@
         <v>127127718</v>
       </c>
       <c r="B30" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B33" t="n">
-        <v>57817</v>
+        <v>57670</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,34 +3846,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R33" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,7 +3918,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,10 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B34" t="n">
-        <v>57670</v>
+        <v>57817</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,42 +3956,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R34" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4050,7 +4050,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>127147802</v>
       </c>
       <c r="B36" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127147809</v>
       </c>
       <c r="B37" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>127147801</v>
       </c>
       <c r="B38" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127147810</v>
       </c>
       <c r="B39" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>127147805</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127147800</v>
       </c>
       <c r="B41" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>127147803</v>
       </c>
       <c r="B42" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>127147799</v>
       </c>
       <c r="B43" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>127147806</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>127147807</v>
       </c>
       <c r="B45" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5146,6 +5146,112 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127268836</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92133</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>253810</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skorpgrynna</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dichostereum boreale</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Pouzar) Ginns &amp; M.N.L.Lefebvre</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Korpnäset, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>786940</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7146494</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127074321</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127074070</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127073751</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127074243</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127074706</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127073807</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127074790</v>
       </c>
       <c r="B8" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>127073629</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127075032</v>
       </c>
       <c r="B10" t="n">
-        <v>91269</v>
+        <v>91275</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>127074190</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,32 +1749,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127127722</v>
+        <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>58488</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>786868</v>
+        <v>786940</v>
       </c>
       <c r="R12" t="n">
-        <v>7146459</v>
+        <v>7146494</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,7 +1828,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1847,32 +1846,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127127713</v>
+        <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>58488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>208245</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>786940</v>
+        <v>786868</v>
       </c>
       <c r="R13" t="n">
-        <v>7146494</v>
+        <v>7146459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,6 +1925,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,53 +2235,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127724</v>
+        <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>57670</v>
+        <v>91683</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786865</v>
+        <v>786885</v>
       </c>
       <c r="R17" t="n">
-        <v>7146487</v>
+        <v>7146464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2345,45 +2332,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127727</v>
+        <v>127127724</v>
       </c>
       <c r="B18" t="n">
-        <v>98353</v>
+        <v>57670</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786967</v>
+        <v>786865</v>
       </c>
       <c r="R18" t="n">
-        <v>7146503</v>
+        <v>7146487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2416,6 +2411,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2442,32 +2442,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127704</v>
+        <v>127127727</v>
       </c>
       <c r="B19" t="n">
-        <v>91677</v>
+        <v>98359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786885</v>
+        <v>786967</v>
       </c>
       <c r="R19" t="n">
-        <v>7146464</v>
+        <v>7146503</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,7 +2542,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>127127703</v>
       </c>
       <c r="B21" t="n">
-        <v>91677</v>
+        <v>91683</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>127127705</v>
       </c>
       <c r="B22" t="n">
-        <v>91677</v>
+        <v>91683</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>127127725</v>
       </c>
       <c r="B23" t="n">
-        <v>91691</v>
+        <v>91697</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>127127701</v>
       </c>
       <c r="B24" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127127822</v>
       </c>
       <c r="B26" t="n">
-        <v>92133</v>
+        <v>92139</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>127127711</v>
       </c>
       <c r="B28" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>127127726</v>
       </c>
       <c r="B29" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>127127718</v>
       </c>
       <c r="B30" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57670</v>
+        <v>57817</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,42 +3846,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R33" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3918,7 +3910,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3945,10 +3937,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57817</v>
+        <v>57670</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3956,34 +3948,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R34" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4050,7 +4050,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>127147802</v>
       </c>
       <c r="B36" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127147809</v>
       </c>
       <c r="B37" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>127147801</v>
       </c>
       <c r="B38" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127147810</v>
       </c>
       <c r="B39" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>127147805</v>
       </c>
       <c r="B40" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127147800</v>
       </c>
       <c r="B41" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>127147803</v>
       </c>
       <c r="B42" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>127147799</v>
       </c>
       <c r="B43" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>127147806</v>
       </c>
       <c r="B44" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>127147807</v>
       </c>
       <c r="B45" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>127268836</v>
       </c>
       <c r="B46" t="n">
-        <v>92133</v>
+        <v>92139</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1535,32 +1535,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127075032</v>
+        <v>127074190</v>
       </c>
       <c r="B10" t="n">
-        <v>91275</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786917</v>
+        <v>786967</v>
       </c>
       <c r="R10" t="n">
-        <v>7146541</v>
+        <v>7146521</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,32 +1642,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127074190</v>
+        <v>127075032</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>91275</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>786967</v>
+        <v>786917</v>
       </c>
       <c r="R11" t="n">
-        <v>7146521</v>
+        <v>7146541</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B14" t="n">
-        <v>91325</v>
+        <v>58516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R14" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B15" t="n">
-        <v>58516</v>
+        <v>91325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R15" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,32 +2235,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127704</v>
+        <v>127127727</v>
       </c>
       <c r="B17" t="n">
-        <v>91683</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786885</v>
+        <v>786967</v>
       </c>
       <c r="R17" t="n">
-        <v>7146464</v>
+        <v>7146503</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,53 +2332,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127724</v>
+        <v>127127704</v>
       </c>
       <c r="B18" t="n">
-        <v>57670</v>
+        <v>91683</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786865</v>
+        <v>786885</v>
       </c>
       <c r="R18" t="n">
-        <v>7146487</v>
+        <v>7146464</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,11 +2403,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2442,45 +2429,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127727</v>
+        <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>98359</v>
+        <v>57670</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100048</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786967</v>
+        <v>786865</v>
       </c>
       <c r="R19" t="n">
-        <v>7146503</v>
+        <v>7146487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,6 +2508,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2936,45 +2936,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127701</v>
+        <v>127127716</v>
       </c>
       <c r="B24" t="n">
-        <v>91290</v>
+        <v>57654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786936</v>
+        <v>786907</v>
       </c>
       <c r="R24" t="n">
-        <v>7146471</v>
+        <v>7146524</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,53 +3041,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127716</v>
+        <v>127127701</v>
       </c>
       <c r="B25" t="n">
-        <v>57654</v>
+        <v>91290</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786907</v>
+        <v>786936</v>
       </c>
       <c r="R25" t="n">
-        <v>7146524</v>
+        <v>7146471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B33" t="n">
-        <v>57817</v>
+        <v>57670</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,34 +3846,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R33" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,7 +3918,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,10 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B34" t="n">
-        <v>57670</v>
+        <v>57817</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,42 +3956,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R34" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1535,32 +1535,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127074190</v>
+        <v>127075032</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>91275</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786967</v>
+        <v>786917</v>
       </c>
       <c r="R10" t="n">
-        <v>7146521</v>
+        <v>7146541</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,32 +1642,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127075032</v>
+        <v>127074190</v>
       </c>
       <c r="B11" t="n">
-        <v>91275</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>786917</v>
+        <v>786967</v>
       </c>
       <c r="R11" t="n">
-        <v>7146541</v>
+        <v>7146521</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2235,32 +2235,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127727</v>
+        <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>91683</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786967</v>
+        <v>786885</v>
       </c>
       <c r="R17" t="n">
-        <v>7146503</v>
+        <v>7146464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,45 +2332,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127704</v>
+        <v>127127724</v>
       </c>
       <c r="B18" t="n">
-        <v>91683</v>
+        <v>57670</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786885</v>
+        <v>786865</v>
       </c>
       <c r="R18" t="n">
-        <v>7146464</v>
+        <v>7146487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2403,6 +2411,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,53 +2442,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127724</v>
+        <v>127127727</v>
       </c>
       <c r="B19" t="n">
-        <v>57670</v>
+        <v>98359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100048</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786865</v>
+        <v>786967</v>
       </c>
       <c r="R19" t="n">
-        <v>7146487</v>
+        <v>7146503</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,11 +2513,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2830,48 +2830,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127725</v>
+        <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91697</v>
+        <v>91290</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1505</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786938</v>
+        <v>786936</v>
       </c>
       <c r="R23" t="n">
-        <v>7146481</v>
+        <v>7146471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2906,18 +2903,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3041,45 +3032,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127701</v>
+        <v>127127725</v>
       </c>
       <c r="B25" t="n">
-        <v>91290</v>
+        <v>91697</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1505</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786936</v>
+        <v>786938</v>
       </c>
       <c r="R25" t="n">
-        <v>7146471</v>
+        <v>7146481</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,12 +3108,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91325</v>
+        <v>91343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R28" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91343</v>
+        <v>91325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R29" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127127718</v>
+        <v>127127715</v>
       </c>
       <c r="B30" t="n">
-        <v>91621</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,34 +3546,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>786936</v>
+        <v>786863</v>
       </c>
       <c r="R30" t="n">
-        <v>7146535</v>
+        <v>7146415</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,27 +3640,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127127715</v>
+        <v>127127721</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>58488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>208245</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3661,24 +3669,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>786863</v>
+        <v>786879</v>
       </c>
       <c r="R31" t="n">
-        <v>7146415</v>
+        <v>7146436</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3719,6 +3719,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3737,32 +3738,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127127721</v>
+        <v>127127718</v>
       </c>
       <c r="B32" t="n">
-        <v>58488</v>
+        <v>91621</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>208245</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3772,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>786879</v>
+        <v>786936</v>
       </c>
       <c r="R32" t="n">
-        <v>7146436</v>
+        <v>7146535</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3816,7 +3817,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127074321</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127074070</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127073751</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127074243</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127074706</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127073807</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127074790</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>127073629</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127075032</v>
       </c>
       <c r="B10" t="n">
-        <v>91275</v>
+        <v>91276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>127074190</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>58516</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R14" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>91325</v>
+        <v>58516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R15" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>127127727</v>
       </c>
       <c r="B19" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127127703</v>
+        <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>786966</v>
+        <v>786856</v>
       </c>
       <c r="R21" t="n">
-        <v>7146509</v>
+        <v>7146424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127127705</v>
+        <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>786856</v>
+        <v>786966</v>
       </c>
       <c r="R22" t="n">
-        <v>7146424</v>
+        <v>7146509</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,7 +2833,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,42 +2927,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127716</v>
+        <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>57654</v>
+        <v>91698</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1505</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2970,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786907</v>
+        <v>786938</v>
       </c>
       <c r="R24" t="n">
-        <v>7146524</v>
+        <v>7146481</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3008,12 +3003,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3032,37 +3033,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127725</v>
+        <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>91697</v>
+        <v>57654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1505</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3070,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786938</v>
+        <v>786907</v>
       </c>
       <c r="R25" t="n">
-        <v>7146481</v>
+        <v>7146524</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,18 +3114,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>127127822</v>
       </c>
       <c r="B26" t="n">
-        <v>92139</v>
+        <v>92140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B28" t="n">
-        <v>91343</v>
+        <v>91326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R28" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B29" t="n">
-        <v>91325</v>
+        <v>91344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R29" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127127715</v>
+        <v>127127718</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>91622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,42 +3546,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>786863</v>
+        <v>786936</v>
       </c>
       <c r="R30" t="n">
-        <v>7146415</v>
+        <v>7146535</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,27 +3632,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127127721</v>
+        <v>127127715</v>
       </c>
       <c r="B31" t="n">
-        <v>58488</v>
+        <v>57654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208245</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3669,16 +3661,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>786879</v>
+        <v>786863</v>
       </c>
       <c r="R31" t="n">
-        <v>7146436</v>
+        <v>7146415</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3719,7 +3719,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3738,32 +3737,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127127718</v>
+        <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>91621</v>
+        <v>58488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>208245</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3773,10 +3772,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>786936</v>
+        <v>786879</v>
       </c>
       <c r="R32" t="n">
-        <v>7146535</v>
+        <v>7146436</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3817,6 +3816,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>127147802</v>
       </c>
       <c r="B36" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127147809</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>127147801</v>
       </c>
       <c r="B38" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127147810</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>127147805</v>
       </c>
       <c r="B40" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127147800</v>
       </c>
       <c r="B41" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>127147803</v>
       </c>
       <c r="B42" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>127147799</v>
       </c>
       <c r="B43" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>127147806</v>
       </c>
       <c r="B44" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>127147807</v>
       </c>
       <c r="B45" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>127268836</v>
       </c>
       <c r="B46" t="n">
-        <v>92139</v>
+        <v>92140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127074790</v>
+        <v>127073629</v>
       </c>
       <c r="B8" t="n">
-        <v>91780</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1328,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786929</v>
+        <v>786926</v>
       </c>
       <c r="R8" t="n">
-        <v>7146554</v>
+        <v>7146477</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1424,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127073629</v>
+        <v>127074790</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>91780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,38 +1439,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786926</v>
+        <v>786929</v>
       </c>
       <c r="R9" t="n">
-        <v>7146477</v>
+        <v>7146554</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127073629</v>
+        <v>127074790</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>91780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,38 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786926</v>
+        <v>786929</v>
       </c>
       <c r="R8" t="n">
-        <v>7146477</v>
+        <v>7146554</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1428,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127074790</v>
+        <v>127073629</v>
       </c>
       <c r="B9" t="n">
-        <v>91780</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,34 +1435,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786929</v>
+        <v>786926</v>
       </c>
       <c r="R9" t="n">
-        <v>7146554</v>
+        <v>7146477</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>58516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R14" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B15" t="n">
-        <v>58516</v>
+        <v>91326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R15" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,45 +2235,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127704</v>
+        <v>127127724</v>
       </c>
       <c r="B17" t="n">
-        <v>91684</v>
+        <v>57670</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786885</v>
+        <v>786865</v>
       </c>
       <c r="R17" t="n">
-        <v>7146464</v>
+        <v>7146487</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2314,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,53 +2345,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127724</v>
+        <v>127127704</v>
       </c>
       <c r="B18" t="n">
-        <v>57670</v>
+        <v>91684</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786865</v>
+        <v>786885</v>
       </c>
       <c r="R18" t="n">
-        <v>7146487</v>
+        <v>7146464</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,11 +2416,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2830,45 +2830,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127701</v>
+        <v>127127716</v>
       </c>
       <c r="B23" t="n">
-        <v>91291</v>
+        <v>57654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786936</v>
+        <v>786907</v>
       </c>
       <c r="R23" t="n">
-        <v>7146471</v>
+        <v>7146524</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,48 +2935,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127725</v>
+        <v>127127701</v>
       </c>
       <c r="B24" t="n">
-        <v>91698</v>
+        <v>91291</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1505</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786938</v>
+        <v>786936</v>
       </c>
       <c r="R24" t="n">
-        <v>7146481</v>
+        <v>7146471</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,18 +3008,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3033,42 +3032,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127716</v>
+        <v>127127725</v>
       </c>
       <c r="B25" t="n">
-        <v>57654</v>
+        <v>91698</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1505</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3076,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786907</v>
+        <v>786938</v>
       </c>
       <c r="R25" t="n">
-        <v>7146524</v>
+        <v>7146481</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,12 +3108,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3632,27 +3632,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127127715</v>
+        <v>127127721</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>58488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>208245</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3661,24 +3661,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>786863</v>
+        <v>786879</v>
       </c>
       <c r="R31" t="n">
-        <v>7146415</v>
+        <v>7146436</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3719,6 +3711,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3737,27 +3730,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127127721</v>
+        <v>127127715</v>
       </c>
       <c r="B32" t="n">
-        <v>58488</v>
+        <v>57654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>208245</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3766,16 +3759,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>786879</v>
+        <v>786863</v>
       </c>
       <c r="R32" t="n">
-        <v>7146436</v>
+        <v>7146415</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3816,7 +3817,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57670</v>
+        <v>57817</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,42 +3846,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R33" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3918,7 +3910,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3945,10 +3937,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57817</v>
+        <v>57670</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3956,34 +3948,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R34" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4445,7 +4445,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127147810</v>
+        <v>127147805</v>
       </c>
       <c r="B39" t="n">
         <v>98443</v>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>786942</v>
+        <v>786981</v>
       </c>
       <c r="R39" t="n">
-        <v>7146469</v>
+        <v>7146502</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127147805</v>
+        <v>127147810</v>
       </c>
       <c r="B40" t="n">
         <v>98443</v>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>786981</v>
+        <v>786942</v>
       </c>
       <c r="R40" t="n">
-        <v>7146502</v>
+        <v>7146469</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1535,32 +1535,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127075032</v>
+        <v>127074190</v>
       </c>
       <c r="B10" t="n">
-        <v>91276</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786917</v>
+        <v>786967</v>
       </c>
       <c r="R10" t="n">
-        <v>7146541</v>
+        <v>7146521</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,32 +1642,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127074190</v>
+        <v>127075032</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>91276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>786967</v>
+        <v>786917</v>
       </c>
       <c r="R11" t="n">
-        <v>7146521</v>
+        <v>7146541</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2235,53 +2235,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127724</v>
+        <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>57670</v>
+        <v>91684</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786865</v>
+        <v>786885</v>
       </c>
       <c r="R17" t="n">
-        <v>7146487</v>
+        <v>7146464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2345,32 +2332,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127704</v>
+        <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>91684</v>
+        <v>98360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2380,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786885</v>
+        <v>786967</v>
       </c>
       <c r="R18" t="n">
-        <v>7146464</v>
+        <v>7146503</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,45 +2429,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127727</v>
+        <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>57670</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100048</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786967</v>
+        <v>786865</v>
       </c>
       <c r="R19" t="n">
-        <v>7146503</v>
+        <v>7146487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,6 +2508,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2830,53 +2830,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127716</v>
+        <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>91291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786907</v>
+        <v>786936</v>
       </c>
       <c r="R23" t="n">
-        <v>7146524</v>
+        <v>7146471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2935,45 +2927,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127701</v>
+        <v>127127716</v>
       </c>
       <c r="B24" t="n">
-        <v>91291</v>
+        <v>57654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786936</v>
+        <v>786907</v>
       </c>
       <c r="R24" t="n">
-        <v>7146471</v>
+        <v>7146524</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91326</v>
+        <v>91344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R28" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91344</v>
+        <v>91326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R29" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B33" t="n">
-        <v>57817</v>
+        <v>57670</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,34 +3846,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R33" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,7 +3918,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,10 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B34" t="n">
-        <v>57670</v>
+        <v>57817</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,42 +3956,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R34" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4848,32 +4848,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127147799</v>
+        <v>127147806</v>
       </c>
       <c r="B43" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>786903</v>
+        <v>786973</v>
       </c>
       <c r="R43" t="n">
-        <v>7146506</v>
+        <v>7146477</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,6 +4919,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4945,32 +4950,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127147806</v>
+        <v>127147799</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4980,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>786973</v>
+        <v>786903</v>
       </c>
       <c r="R44" t="n">
-        <v>7146477</v>
+        <v>7146506</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,11 +5021,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1535,32 +1535,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127074190</v>
+        <v>127075032</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>91276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786967</v>
+        <v>786917</v>
       </c>
       <c r="R10" t="n">
-        <v>7146521</v>
+        <v>7146541</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,32 +1642,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127075032</v>
+        <v>127074190</v>
       </c>
       <c r="B11" t="n">
-        <v>91276</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>786917</v>
+        <v>786967</v>
       </c>
       <c r="R11" t="n">
-        <v>7146541</v>
+        <v>7146521</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2830,45 +2830,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127701</v>
+        <v>127127716</v>
       </c>
       <c r="B23" t="n">
-        <v>91291</v>
+        <v>57654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786936</v>
+        <v>786907</v>
       </c>
       <c r="R23" t="n">
-        <v>7146471</v>
+        <v>7146524</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,53 +2935,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127716</v>
+        <v>127127701</v>
       </c>
       <c r="B24" t="n">
-        <v>57654</v>
+        <v>91291</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786907</v>
+        <v>786936</v>
       </c>
       <c r="R24" t="n">
-        <v>7146524</v>
+        <v>7146471</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3632,27 +3632,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127127721</v>
+        <v>127127715</v>
       </c>
       <c r="B31" t="n">
-        <v>58488</v>
+        <v>57654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208245</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3661,16 +3661,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>786879</v>
+        <v>786863</v>
       </c>
       <c r="R31" t="n">
-        <v>7146436</v>
+        <v>7146415</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3711,7 +3719,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3730,27 +3737,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127127715</v>
+        <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>57654</v>
+        <v>58488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>208245</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3759,24 +3766,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>786863</v>
+        <v>786879</v>
       </c>
       <c r="R32" t="n">
-        <v>7146415</v>
+        <v>7146436</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3817,6 +3816,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57670</v>
+        <v>57817</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,42 +3846,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R33" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3918,7 +3910,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3945,10 +3937,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57817</v>
+        <v>57670</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3956,34 +3948,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R34" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127074321</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127074070</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127073751</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127074243</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127074706</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127073807</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127074790</v>
+        <v>127073629</v>
       </c>
       <c r="B8" t="n">
-        <v>91780</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1328,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786929</v>
+        <v>786926</v>
       </c>
       <c r="R8" t="n">
-        <v>7146554</v>
+        <v>7146477</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1424,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127073629</v>
+        <v>127074790</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>91784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,38 +1439,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786926</v>
+        <v>786929</v>
       </c>
       <c r="R9" t="n">
-        <v>7146477</v>
+        <v>7146554</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1538,7 +1538,7 @@
         <v>127075032</v>
       </c>
       <c r="B10" t="n">
-        <v>91276</v>
+        <v>91280</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>127074190</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,32 +1749,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127127713</v>
+        <v>127127722</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>58492</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>208245</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>786940</v>
+        <v>786868</v>
       </c>
       <c r="R12" t="n">
-        <v>7146494</v>
+        <v>7146459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,6 +1828,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1846,32 +1847,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127127722</v>
+        <v>127127713</v>
       </c>
       <c r="B13" t="n">
-        <v>58488</v>
+        <v>57821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>786868</v>
+        <v>786940</v>
       </c>
       <c r="R13" t="n">
-        <v>7146459</v>
+        <v>7146494</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,7 +1926,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>58516</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R14" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>58520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R15" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,45 +2235,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127704</v>
+        <v>127127724</v>
       </c>
       <c r="B17" t="n">
-        <v>91684</v>
+        <v>57674</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786885</v>
+        <v>786865</v>
       </c>
       <c r="R17" t="n">
-        <v>7146464</v>
+        <v>7146487</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2314,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,7 +2348,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2429,53 +2442,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127724</v>
+        <v>127127704</v>
       </c>
       <c r="B19" t="n">
-        <v>57670</v>
+        <v>91688</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100048</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786865</v>
+        <v>786885</v>
       </c>
       <c r="R19" t="n">
-        <v>7146487</v>
+        <v>7146464</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,11 +2513,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2542,7 +2542,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91684</v>
+        <v>91688</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91684</v>
+        <v>91688</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,42 +2830,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127716</v>
+        <v>127127725</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>91702</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1505</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2873,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786907</v>
+        <v>786938</v>
       </c>
       <c r="R23" t="n">
-        <v>7146524</v>
+        <v>7146481</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2911,12 +2906,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2938,7 +2939,7 @@
         <v>127127701</v>
       </c>
       <c r="B24" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,37 +3033,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127725</v>
+        <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>91698</v>
+        <v>57658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1505</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3070,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786938</v>
+        <v>786907</v>
       </c>
       <c r="R25" t="n">
-        <v>7146481</v>
+        <v>7146524</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,18 +3114,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>127127822</v>
       </c>
       <c r="B26" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B28" t="n">
-        <v>91344</v>
+        <v>91330</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R28" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B29" t="n">
-        <v>91326</v>
+        <v>91348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R29" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,7 +3538,7 @@
         <v>127127718</v>
       </c>
       <c r="B30" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>127127715</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>58488</v>
+        <v>58492</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57670</v>
+        <v>57674</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>127147802</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127147809</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>127147801</v>
       </c>
       <c r="B38" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4445,10 +4445,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127147805</v>
+        <v>127147810</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>786981</v>
+        <v>786942</v>
       </c>
       <c r="R39" t="n">
-        <v>7146502</v>
+        <v>7146469</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,10 +4547,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127147810</v>
+        <v>127147805</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>786942</v>
+        <v>786981</v>
       </c>
       <c r="R40" t="n">
-        <v>7146469</v>
+        <v>7146502</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,7 +4652,7 @@
         <v>127147800</v>
       </c>
       <c r="B41" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>127147803</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>127147806</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>127147799</v>
       </c>
       <c r="B44" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>127147807</v>
       </c>
       <c r="B45" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>127268836</v>
       </c>
       <c r="B46" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1749,32 +1749,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127127722</v>
+        <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>58492</v>
+        <v>57821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>786868</v>
+        <v>786940</v>
       </c>
       <c r="R12" t="n">
-        <v>7146459</v>
+        <v>7146494</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,7 +1828,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1847,32 +1846,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127127713</v>
+        <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>57821</v>
+        <v>58492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>208245</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>786940</v>
+        <v>786868</v>
       </c>
       <c r="R13" t="n">
-        <v>7146494</v>
+        <v>7146459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,6 +1925,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2235,53 +2235,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127724</v>
+        <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>57674</v>
+        <v>91688</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786865</v>
+        <v>786885</v>
       </c>
       <c r="R17" t="n">
-        <v>7146487</v>
+        <v>7146464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2442,45 +2429,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127704</v>
+        <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>91688</v>
+        <v>57674</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>100048</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786885</v>
+        <v>786865</v>
       </c>
       <c r="R19" t="n">
-        <v>7146464</v>
+        <v>7146487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,6 +2508,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2830,37 +2830,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127725</v>
+        <v>127127716</v>
       </c>
       <c r="B23" t="n">
-        <v>91702</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1505</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2868,10 +2873,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786938</v>
+        <v>786907</v>
       </c>
       <c r="R23" t="n">
-        <v>7146481</v>
+        <v>7146524</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2906,18 +2911,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2936,45 +2935,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127701</v>
+        <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91295</v>
+        <v>91702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1505</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786936</v>
+        <v>786938</v>
       </c>
       <c r="R24" t="n">
-        <v>7146471</v>
+        <v>7146481</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,12 +3011,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3033,53 +3041,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127716</v>
+        <v>127127701</v>
       </c>
       <c r="B25" t="n">
-        <v>57658</v>
+        <v>91295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786907</v>
+        <v>786936</v>
       </c>
       <c r="R25" t="n">
-        <v>7146524</v>
+        <v>7146471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R28" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R29" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,27 +3632,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127127715</v>
+        <v>127127721</v>
       </c>
       <c r="B31" t="n">
-        <v>57658</v>
+        <v>58492</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>208245</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3661,24 +3661,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>786863</v>
+        <v>786879</v>
       </c>
       <c r="R31" t="n">
-        <v>7146415</v>
+        <v>7146436</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3719,6 +3711,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3737,27 +3730,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127127721</v>
+        <v>127127715</v>
       </c>
       <c r="B32" t="n">
-        <v>58492</v>
+        <v>57658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>208245</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3766,16 +3759,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>786879</v>
+        <v>786863</v>
       </c>
       <c r="R32" t="n">
-        <v>7146436</v>
+        <v>7146415</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3816,7 +3817,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>58520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R14" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B15" t="n">
-        <v>58520</v>
+        <v>91330</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R15" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B33" t="n">
-        <v>57821</v>
+        <v>57674</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,34 +3846,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R33" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,7 +3918,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,10 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B34" t="n">
-        <v>57674</v>
+        <v>57821</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,42 +3956,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R34" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127074321</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127074070</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127073751</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127074243</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127074706</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127073807</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127073629</v>
+        <v>127074790</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>91784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,38 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786926</v>
+        <v>786929</v>
       </c>
       <c r="R8" t="n">
-        <v>7146477</v>
+        <v>7146554</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1428,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127074790</v>
+        <v>127073629</v>
       </c>
       <c r="B9" t="n">
-        <v>91784</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,34 +1435,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786929</v>
+        <v>786926</v>
       </c>
       <c r="R9" t="n">
-        <v>7146554</v>
+        <v>7146477</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1645,7 +1645,7 @@
         <v>127074190</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>58520</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R14" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>91330</v>
+        <v>58520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R15" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2332,45 +2332,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127727</v>
+        <v>127127724</v>
       </c>
       <c r="B18" t="n">
-        <v>98364</v>
+        <v>57674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786967</v>
+        <v>786865</v>
       </c>
       <c r="R18" t="n">
-        <v>7146503</v>
+        <v>7146487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2403,6 +2411,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,53 +2442,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127724</v>
+        <v>127127727</v>
       </c>
       <c r="B19" t="n">
-        <v>57674</v>
+        <v>98365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100048</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786865</v>
+        <v>786967</v>
       </c>
       <c r="R19" t="n">
-        <v>7146487</v>
+        <v>7146503</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,11 +2513,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2935,48 +2935,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127725</v>
+        <v>127127701</v>
       </c>
       <c r="B24" t="n">
-        <v>91702</v>
+        <v>91295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1505</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786938</v>
+        <v>786936</v>
       </c>
       <c r="R24" t="n">
-        <v>7146481</v>
+        <v>7146471</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3011,18 +3008,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3041,45 +3032,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127701</v>
+        <v>127127725</v>
       </c>
       <c r="B25" t="n">
-        <v>91295</v>
+        <v>91702</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1505</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786936</v>
+        <v>786938</v>
       </c>
       <c r="R25" t="n">
-        <v>7146471</v>
+        <v>7146481</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,12 +3108,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B28" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R28" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R29" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3632,27 +3632,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127127721</v>
+        <v>127127715</v>
       </c>
       <c r="B31" t="n">
-        <v>58492</v>
+        <v>57658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208245</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3661,16 +3661,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>786879</v>
+        <v>786863</v>
       </c>
       <c r="R31" t="n">
-        <v>7146436</v>
+        <v>7146415</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3711,7 +3719,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3730,27 +3737,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127127715</v>
+        <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>57658</v>
+        <v>58492</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>208245</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3759,24 +3766,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>786863</v>
+        <v>786879</v>
       </c>
       <c r="R32" t="n">
-        <v>7146415</v>
+        <v>7146436</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3817,6 +3816,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>127147802</v>
       </c>
       <c r="B36" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127147809</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127147810</v>
       </c>
       <c r="B39" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>127147805</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>127147803</v>
       </c>
       <c r="B42" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>127147806</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>127147807</v>
       </c>
       <c r="B45" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>58520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R14" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B15" t="n">
-        <v>58520</v>
+        <v>91330</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R15" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2830,53 +2830,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127716</v>
+        <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>91295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786907</v>
+        <v>786936</v>
       </c>
       <c r="R23" t="n">
-        <v>7146524</v>
+        <v>7146471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2935,45 +2927,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127701</v>
+        <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91295</v>
+        <v>91702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1505</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786936</v>
+        <v>786938</v>
       </c>
       <c r="R24" t="n">
-        <v>7146471</v>
+        <v>7146481</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3008,12 +3003,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3032,37 +3033,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127725</v>
+        <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>91702</v>
+        <v>57658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1505</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3070,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786938</v>
+        <v>786907</v>
       </c>
       <c r="R25" t="n">
-        <v>7146481</v>
+        <v>7146524</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,18 +3114,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127074321</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127074070</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127073751</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127074243</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127074706</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127073807</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127074790</v>
       </c>
       <c r="B8" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>127073629</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127075032</v>
       </c>
       <c r="B10" t="n">
-        <v>91280</v>
+        <v>91282</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>127074190</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>58492</v>
+        <v>58494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>127127702</v>
       </c>
       <c r="B14" t="n">
-        <v>58520</v>
+        <v>58522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>127127709</v>
       </c>
       <c r="B15" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,45 +2235,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127704</v>
+        <v>127127724</v>
       </c>
       <c r="B17" t="n">
-        <v>91688</v>
+        <v>57676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786885</v>
+        <v>786865</v>
       </c>
       <c r="R17" t="n">
-        <v>7146464</v>
+        <v>7146487</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2314,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,53 +2345,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127724</v>
+        <v>127127704</v>
       </c>
       <c r="B18" t="n">
-        <v>57674</v>
+        <v>91690</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786865</v>
+        <v>786885</v>
       </c>
       <c r="R18" t="n">
-        <v>7146487</v>
+        <v>7146464</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,11 +2416,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2445,7 +2445,7 @@
         <v>127127727</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,45 +2830,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127701</v>
+        <v>127127725</v>
       </c>
       <c r="B23" t="n">
-        <v>91295</v>
+        <v>91704</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1505</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786936</v>
+        <v>786938</v>
       </c>
       <c r="R23" t="n">
-        <v>7146471</v>
+        <v>7146481</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,12 +2906,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2927,37 +2936,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127725</v>
+        <v>127127716</v>
       </c>
       <c r="B24" t="n">
-        <v>91702</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1505</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2965,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786938</v>
+        <v>786907</v>
       </c>
       <c r="R24" t="n">
-        <v>7146481</v>
+        <v>7146524</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,18 +3017,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3033,53 +3041,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127716</v>
+        <v>127127701</v>
       </c>
       <c r="B25" t="n">
-        <v>57658</v>
+        <v>91297</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786907</v>
+        <v>786936</v>
       </c>
       <c r="R25" t="n">
-        <v>7146524</v>
+        <v>7146471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
         <v>127127822</v>
       </c>
       <c r="B26" t="n">
-        <v>92144</v>
+        <v>92146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>127127711</v>
       </c>
       <c r="B28" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>127127726</v>
       </c>
       <c r="B29" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127127718</v>
+        <v>127127715</v>
       </c>
       <c r="B30" t="n">
-        <v>91626</v>
+        <v>57660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,34 +3546,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>786936</v>
+        <v>786863</v>
       </c>
       <c r="R30" t="n">
-        <v>7146535</v>
+        <v>7146415</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,10 +3640,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127127715</v>
+        <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>57658</v>
+        <v>91628</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,42 +3651,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>786863</v>
+        <v>786936</v>
       </c>
       <c r="R31" t="n">
-        <v>7146415</v>
+        <v>7146535</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
         <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>58492</v>
+        <v>58494</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>127127723</v>
       </c>
       <c r="B33" t="n">
-        <v>57674</v>
+        <v>57676</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>127127712</v>
       </c>
       <c r="B34" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>127147802</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127147809</v>
       </c>
       <c r="B37" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>127147801</v>
       </c>
       <c r="B38" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127147810</v>
       </c>
       <c r="B39" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>127147805</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127147800</v>
       </c>
       <c r="B41" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>127147803</v>
       </c>
       <c r="B42" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>127147806</v>
       </c>
       <c r="B43" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>127147799</v>
       </c>
       <c r="B44" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>127147807</v>
       </c>
       <c r="B45" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>127268836</v>
       </c>
       <c r="B46" t="n">
-        <v>92144</v>
+        <v>92146</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127074790</v>
+        <v>127073629</v>
       </c>
       <c r="B8" t="n">
-        <v>91786</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1328,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786929</v>
+        <v>786926</v>
       </c>
       <c r="R8" t="n">
-        <v>7146554</v>
+        <v>7146477</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1424,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127073629</v>
+        <v>127074790</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>91786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,38 +1439,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786926</v>
+        <v>786929</v>
       </c>
       <c r="R9" t="n">
-        <v>7146477</v>
+        <v>7146554</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1749,32 +1749,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127127713</v>
+        <v>127127722</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>58494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>208245</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>786940</v>
+        <v>786868</v>
       </c>
       <c r="R12" t="n">
-        <v>7146494</v>
+        <v>7146459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,6 +1828,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1846,32 +1847,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127127722</v>
+        <v>127127713</v>
       </c>
       <c r="B13" t="n">
-        <v>58494</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>786868</v>
+        <v>786940</v>
       </c>
       <c r="R13" t="n">
-        <v>7146459</v>
+        <v>7146494</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,7 +1926,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>58522</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R14" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>91332</v>
+        <v>58522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R15" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,53 +2235,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127724</v>
+        <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>57676</v>
+        <v>91690</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786865</v>
+        <v>786885</v>
       </c>
       <c r="R17" t="n">
-        <v>7146487</v>
+        <v>7146464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2345,32 +2332,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127704</v>
+        <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>91690</v>
+        <v>98367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2380,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786885</v>
+        <v>786967</v>
       </c>
       <c r="R18" t="n">
-        <v>7146464</v>
+        <v>7146503</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,45 +2429,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127727</v>
+        <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>98367</v>
+        <v>57676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100048</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786967</v>
+        <v>786865</v>
       </c>
       <c r="R19" t="n">
-        <v>7146503</v>
+        <v>7146487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,6 +2508,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2830,48 +2830,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127725</v>
+        <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91704</v>
+        <v>91297</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1505</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786938</v>
+        <v>786936</v>
       </c>
       <c r="R23" t="n">
-        <v>7146481</v>
+        <v>7146471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2906,18 +2903,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3041,45 +3032,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127701</v>
+        <v>127127725</v>
       </c>
       <c r="B25" t="n">
-        <v>91297</v>
+        <v>91704</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1505</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786936</v>
+        <v>786938</v>
       </c>
       <c r="R25" t="n">
-        <v>7146471</v>
+        <v>7146481</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,12 +3108,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R28" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R29" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127127715</v>
+        <v>127127718</v>
       </c>
       <c r="B30" t="n">
-        <v>57660</v>
+        <v>91628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,42 +3546,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>786863</v>
+        <v>786936</v>
       </c>
       <c r="R30" t="n">
-        <v>7146415</v>
+        <v>7146535</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127127718</v>
+        <v>127127715</v>
       </c>
       <c r="B31" t="n">
-        <v>91628</v>
+        <v>57660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,34 +3643,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>786936</v>
+        <v>786863</v>
       </c>
       <c r="R31" t="n">
-        <v>7146535</v>
+        <v>7146415</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57676</v>
+        <v>57823</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,42 +3846,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R33" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3918,7 +3910,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3945,10 +3937,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57823</v>
+        <v>57676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3956,34 +3948,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R34" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4848,32 +4848,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127147806</v>
+        <v>127147799</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>786973</v>
+        <v>786903</v>
       </c>
       <c r="R43" t="n">
-        <v>7146477</v>
+        <v>7146506</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,11 +4919,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,32 +4945,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127147799</v>
+        <v>127147806</v>
       </c>
       <c r="B44" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4980,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>786903</v>
+        <v>786973</v>
       </c>
       <c r="R44" t="n">
-        <v>7146506</v>
+        <v>7146477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5021,6 +5016,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -2332,45 +2332,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127727</v>
+        <v>127127724</v>
       </c>
       <c r="B18" t="n">
-        <v>98367</v>
+        <v>57676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786967</v>
+        <v>786865</v>
       </c>
       <c r="R18" t="n">
-        <v>7146503</v>
+        <v>7146487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2403,6 +2411,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,53 +2442,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127724</v>
+        <v>127127727</v>
       </c>
       <c r="B19" t="n">
-        <v>57676</v>
+        <v>98367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100048</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786865</v>
+        <v>786967</v>
       </c>
       <c r="R19" t="n">
-        <v>7146487</v>
+        <v>7146503</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,11 +2513,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4848,32 +4848,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127147799</v>
+        <v>127147806</v>
       </c>
       <c r="B43" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>786903</v>
+        <v>786973</v>
       </c>
       <c r="R43" t="n">
-        <v>7146506</v>
+        <v>7146477</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,6 +4919,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4945,32 +4950,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127147806</v>
+        <v>127147799</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4980,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>786973</v>
+        <v>786903</v>
       </c>
       <c r="R44" t="n">
-        <v>7146477</v>
+        <v>7146506</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,11 +5021,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127073629</v>
+        <v>127074790</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>91786</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,38 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786926</v>
+        <v>786929</v>
       </c>
       <c r="R8" t="n">
-        <v>7146477</v>
+        <v>7146554</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1428,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127074790</v>
+        <v>127073629</v>
       </c>
       <c r="B9" t="n">
-        <v>91786</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,34 +1435,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786929</v>
+        <v>786926</v>
       </c>
       <c r="R9" t="n">
-        <v>7146554</v>
+        <v>7146477</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1535,32 +1535,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127075032</v>
+        <v>127074190</v>
       </c>
       <c r="B10" t="n">
-        <v>91282</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786917</v>
+        <v>786967</v>
       </c>
       <c r="R10" t="n">
-        <v>7146541</v>
+        <v>7146521</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,32 +1642,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127074190</v>
+        <v>127075032</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>91282</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>786967</v>
+        <v>786917</v>
       </c>
       <c r="R11" t="n">
-        <v>7146521</v>
+        <v>7146541</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,32 +1749,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127127722</v>
+        <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>58494</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>786868</v>
+        <v>786940</v>
       </c>
       <c r="R12" t="n">
-        <v>7146459</v>
+        <v>7146494</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,7 +1828,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1847,32 +1846,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127127713</v>
+        <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>58494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>208245</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>786940</v>
+        <v>786868</v>
       </c>
       <c r="R13" t="n">
-        <v>7146494</v>
+        <v>7146459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,6 +1925,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2927,42 +2927,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127716</v>
+        <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>57660</v>
+        <v>91704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1505</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2970,10 +2965,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786907</v>
+        <v>786938</v>
       </c>
       <c r="R24" t="n">
-        <v>7146524</v>
+        <v>7146481</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3008,12 +3003,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3032,37 +3033,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127725</v>
+        <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>91704</v>
+        <v>57660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1505</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3070,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786938</v>
+        <v>786907</v>
       </c>
       <c r="R25" t="n">
-        <v>7146481</v>
+        <v>7146524</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,18 +3114,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R28" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B29" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R29" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B33" t="n">
-        <v>57823</v>
+        <v>57676</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,34 +3846,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R33" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,7 +3918,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,10 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B34" t="n">
-        <v>57676</v>
+        <v>57823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,42 +3956,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R34" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127074321</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127074070</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127073751</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127074243</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127074706</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127073807</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127074790</v>
+        <v>127073629</v>
       </c>
       <c r="B8" t="n">
-        <v>91786</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1328,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786929</v>
+        <v>786926</v>
       </c>
       <c r="R8" t="n">
-        <v>7146554</v>
+        <v>7146477</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1424,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127073629</v>
+        <v>127074790</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>91792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,38 +1439,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786926</v>
+        <v>786929</v>
       </c>
       <c r="R9" t="n">
-        <v>7146477</v>
+        <v>7146554</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1535,32 +1535,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127074190</v>
+        <v>127075032</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>91288</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786967</v>
+        <v>786917</v>
       </c>
       <c r="R10" t="n">
-        <v>7146521</v>
+        <v>7146541</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,32 +1642,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127075032</v>
+        <v>127074190</v>
       </c>
       <c r="B11" t="n">
-        <v>91282</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>786917</v>
+        <v>786967</v>
       </c>
       <c r="R11" t="n">
-        <v>7146541</v>
+        <v>7146521</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>58522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R14" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B15" t="n">
-        <v>58522</v>
+        <v>91338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R15" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,53 +2332,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127724</v>
+        <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>57676</v>
+        <v>98373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786865</v>
+        <v>786967</v>
       </c>
       <c r="R18" t="n">
-        <v>7146487</v>
+        <v>7146503</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,11 +2403,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2442,45 +2429,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127727</v>
+        <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>98367</v>
+        <v>57676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100048</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786967</v>
+        <v>786865</v>
       </c>
       <c r="R19" t="n">
-        <v>7146503</v>
+        <v>7146487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,6 +2508,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2542,7 +2542,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,45 +2830,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127701</v>
+        <v>127127716</v>
       </c>
       <c r="B23" t="n">
-        <v>91297</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786936</v>
+        <v>786907</v>
       </c>
       <c r="R23" t="n">
-        <v>7146471</v>
+        <v>7146524</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,48 +2935,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127725</v>
+        <v>127127701</v>
       </c>
       <c r="B24" t="n">
-        <v>91704</v>
+        <v>91303</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1505</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786938</v>
+        <v>786936</v>
       </c>
       <c r="R24" t="n">
-        <v>7146481</v>
+        <v>7146471</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,18 +3008,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3033,42 +3032,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127716</v>
+        <v>127127725</v>
       </c>
       <c r="B25" t="n">
-        <v>57660</v>
+        <v>91710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1505</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3076,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786907</v>
+        <v>786938</v>
       </c>
       <c r="R25" t="n">
-        <v>7146524</v>
+        <v>7146481</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,12 +3108,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>127127822</v>
       </c>
       <c r="B26" t="n">
-        <v>92146</v>
+        <v>92152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91332</v>
+        <v>91356</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R28" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91350</v>
+        <v>91338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R29" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,7 +3538,7 @@
         <v>127127718</v>
       </c>
       <c r="B30" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>127147802</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127147809</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>127147801</v>
       </c>
       <c r="B38" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127147810</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>127147805</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127147800</v>
       </c>
       <c r="B41" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>127147803</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4848,32 +4848,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127147806</v>
+        <v>127147799</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>91338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>786973</v>
+        <v>786903</v>
       </c>
       <c r="R43" t="n">
-        <v>7146477</v>
+        <v>7146506</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,11 +4919,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,32 +4945,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127147799</v>
+        <v>127147806</v>
       </c>
       <c r="B44" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4980,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>786903</v>
+        <v>786973</v>
       </c>
       <c r="R44" t="n">
-        <v>7146506</v>
+        <v>7146477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5021,6 +5016,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5050,7 +5050,7 @@
         <v>127147807</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>127268836</v>
       </c>
       <c r="B46" t="n">
-        <v>92146</v>
+        <v>92152</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127074321</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127074070</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127073751</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127074243</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127074706</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127073807</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127073629</v>
+        <v>127074790</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>91795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,38 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786926</v>
+        <v>786929</v>
       </c>
       <c r="R8" t="n">
-        <v>7146477</v>
+        <v>7146554</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1428,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127074790</v>
+        <v>127073629</v>
       </c>
       <c r="B9" t="n">
-        <v>91792</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,34 +1435,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpnäset, Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786929</v>
+        <v>786926</v>
       </c>
       <c r="R9" t="n">
-        <v>7146554</v>
+        <v>7146477</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1538,7 +1538,7 @@
         <v>127075032</v>
       </c>
       <c r="B10" t="n">
-        <v>91288</v>
+        <v>91291</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>127074190</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>58494</v>
+        <v>58497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>127127702</v>
       </c>
       <c r="B14" t="n">
-        <v>58522</v>
+        <v>58525</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>127127709</v>
       </c>
       <c r="B15" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,45 +2235,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127704</v>
+        <v>127127724</v>
       </c>
       <c r="B17" t="n">
-        <v>91696</v>
+        <v>57679</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786885</v>
+        <v>786865</v>
       </c>
       <c r="R17" t="n">
-        <v>7146464</v>
+        <v>7146487</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2314,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,7 +2348,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2429,53 +2442,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127724</v>
+        <v>127127704</v>
       </c>
       <c r="B19" t="n">
-        <v>57676</v>
+        <v>91699</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100048</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786865</v>
+        <v>786885</v>
       </c>
       <c r="R19" t="n">
-        <v>7146487</v>
+        <v>7146464</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,11 +2513,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2542,7 +2542,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>127127716</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2935,45 +2935,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127127701</v>
+        <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91303</v>
+        <v>91713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1505</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>786936</v>
+        <v>786938</v>
       </c>
       <c r="R24" t="n">
-        <v>7146471</v>
+        <v>7146481</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3008,12 +3011,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3032,48 +3041,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127725</v>
+        <v>127127701</v>
       </c>
       <c r="B25" t="n">
-        <v>91710</v>
+        <v>91306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1505</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786938</v>
+        <v>786936</v>
       </c>
       <c r="R25" t="n">
-        <v>7146481</v>
+        <v>7146471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,18 +3114,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ska skickas på mikroskopering. Skulle kunna vara någon annan Skeletocutis</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>127127822</v>
       </c>
       <c r="B26" t="n">
-        <v>92152</v>
+        <v>92155</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B28" t="n">
-        <v>91356</v>
+        <v>91341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R28" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B29" t="n">
-        <v>91338</v>
+        <v>91359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R29" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,7 +3538,7 @@
         <v>127127718</v>
       </c>
       <c r="B30" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>127127715</v>
       </c>
       <c r="B31" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>58494</v>
+        <v>58497</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57676</v>
+        <v>57826</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,42 +3846,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R33" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3918,7 +3910,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3945,10 +3937,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57823</v>
+        <v>57679</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3956,34 +3948,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R34" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4050,7 +4050,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>127147802</v>
       </c>
       <c r="B36" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127147809</v>
       </c>
       <c r="B37" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>127147801</v>
       </c>
       <c r="B38" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127147810</v>
       </c>
       <c r="B39" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>127147805</v>
       </c>
       <c r="B40" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127147800</v>
       </c>
       <c r="B41" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>127147803</v>
       </c>
       <c r="B42" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4848,32 +4848,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127147799</v>
+        <v>127147806</v>
       </c>
       <c r="B43" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>786903</v>
+        <v>786973</v>
       </c>
       <c r="R43" t="n">
-        <v>7146506</v>
+        <v>7146477</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,6 +4919,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4945,32 +4950,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127147806</v>
+        <v>127147799</v>
       </c>
       <c r="B44" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4980,10 +4985,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>786973</v>
+        <v>786903</v>
       </c>
       <c r="R44" t="n">
-        <v>7146477</v>
+        <v>7146506</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,11 +5021,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5050,7 +5050,7 @@
         <v>127147807</v>
       </c>
       <c r="B45" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>127268836</v>
       </c>
       <c r="B46" t="n">
-        <v>92152</v>
+        <v>92155</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>58497</v>
+        <v>58503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,32 +1944,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127127702</v>
+        <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>58525</v>
+        <v>91349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786932</v>
+        <v>786879</v>
       </c>
       <c r="R14" t="n">
-        <v>7146486</v>
+        <v>7146446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,32 +2041,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127127709</v>
+        <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>91341</v>
+        <v>58531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>208249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786879</v>
+        <v>786932</v>
       </c>
       <c r="R15" t="n">
-        <v>7146446</v>
+        <v>7146486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,53 +2235,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127724</v>
+        <v>127127727</v>
       </c>
       <c r="B17" t="n">
-        <v>57679</v>
+        <v>98384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786865</v>
+        <v>786967</v>
       </c>
       <c r="R17" t="n">
-        <v>7146487</v>
+        <v>7146503</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,11 +2306,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2345,32 +2332,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127727</v>
+        <v>127127704</v>
       </c>
       <c r="B18" t="n">
-        <v>98376</v>
+        <v>91707</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2380,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786967</v>
+        <v>786885</v>
       </c>
       <c r="R18" t="n">
-        <v>7146503</v>
+        <v>7146464</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,45 +2429,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127127704</v>
+        <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>91699</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>100048</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>786885</v>
+        <v>786865</v>
       </c>
       <c r="R19" t="n">
-        <v>7146464</v>
+        <v>7146487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,6 +2508,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2542,7 +2542,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,53 +2830,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127127716</v>
+        <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>91314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>786907</v>
+        <v>786936</v>
       </c>
       <c r="R23" t="n">
-        <v>7146524</v>
+        <v>7146471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,7 +2930,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91713</v>
+        <v>91721</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3041,45 +3033,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127127701</v>
+        <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>91306</v>
+        <v>57669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>786936</v>
+        <v>786907</v>
       </c>
       <c r="R25" t="n">
-        <v>7146471</v>
+        <v>7146524</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
         <v>127127822</v>
       </c>
       <c r="B26" t="n">
-        <v>92155</v>
+        <v>92163</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127127711</v>
+        <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91341</v>
+        <v>91367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>786856</v>
+        <v>786917</v>
       </c>
       <c r="R28" t="n">
-        <v>7146424</v>
+        <v>7146523</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127127726</v>
+        <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91359</v>
+        <v>91349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>786917</v>
+        <v>786856</v>
       </c>
       <c r="R29" t="n">
-        <v>7146523</v>
+        <v>7146424</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127127718</v>
+        <v>127127715</v>
       </c>
       <c r="B30" t="n">
-        <v>91637</v>
+        <v>57669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,34 +3546,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>786936</v>
+        <v>786863</v>
       </c>
       <c r="R30" t="n">
-        <v>7146535</v>
+        <v>7146415</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,10 +3640,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127127715</v>
+        <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>91645</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,42 +3651,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>786863</v>
+        <v>786936</v>
       </c>
       <c r="R31" t="n">
-        <v>7146415</v>
+        <v>7146535</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
         <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>58497</v>
+        <v>58503</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B33" t="n">
-        <v>57826</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,34 +3846,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R33" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,7 +3918,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,10 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B34" t="n">
-        <v>57679</v>
+        <v>57832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,42 +3956,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R34" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4050,7 +4050,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>127147802</v>
       </c>
       <c r="B36" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127147809</v>
       </c>
       <c r="B37" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>127147801</v>
       </c>
       <c r="B38" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127147810</v>
       </c>
       <c r="B39" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>127147805</v>
       </c>
       <c r="B40" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127147800</v>
       </c>
       <c r="B41" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>127147803</v>
       </c>
       <c r="B42" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>127147806</v>
       </c>
       <c r="B43" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>127147799</v>
       </c>
       <c r="B44" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>127147807</v>
       </c>
       <c r="B45" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>127268836</v>
       </c>
       <c r="B46" t="n">
-        <v>92155</v>
+        <v>92163</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -2235,32 +2235,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127127727</v>
+        <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>98384</v>
+        <v>91707</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>786967</v>
+        <v>786885</v>
       </c>
       <c r="R17" t="n">
-        <v>7146503</v>
+        <v>7146464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,32 +2332,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127127704</v>
+        <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>91707</v>
+        <v>98384</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>786885</v>
+        <v>786967</v>
       </c>
       <c r="R18" t="n">
-        <v>7146464</v>
+        <v>7146503</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127127723</v>
+        <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>57832</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,42 +3846,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>786842</v>
+        <v>786876</v>
       </c>
       <c r="R33" t="n">
-        <v>7146482</v>
+        <v>7146487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3918,7 +3910,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3945,10 +3937,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127127712</v>
+        <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57832</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3956,34 +3948,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Korpnäset, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>786876</v>
+        <v>786842</v>
       </c>
       <c r="R34" t="n">
-        <v>7146487</v>
+        <v>7146482</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4147,7 +4147,7 @@
         <v>127147802</v>
       </c>
       <c r="B36" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127147809</v>
       </c>
       <c r="B37" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>127147801</v>
       </c>
       <c r="B38" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127147810</v>
       </c>
       <c r="B39" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>127147805</v>
       </c>
       <c r="B40" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127147800</v>
       </c>
       <c r="B41" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>127147803</v>
       </c>
       <c r="B42" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4848,32 +4848,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127147806</v>
+        <v>127147799</v>
       </c>
       <c r="B43" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>786973</v>
+        <v>786903</v>
       </c>
       <c r="R43" t="n">
-        <v>7146477</v>
+        <v>7146506</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,11 +4919,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,32 +4945,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127147799</v>
+        <v>127147806</v>
       </c>
       <c r="B44" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4985,10 +4980,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>786903</v>
+        <v>786973</v>
       </c>
       <c r="R44" t="n">
-        <v>7146506</v>
+        <v>7146477</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5021,6 +5016,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5050,7 +5050,7 @@
         <v>127147807</v>
       </c>
       <c r="B45" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>127268836</v>
       </c>
       <c r="B46" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,14 +1842,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>58503</v>
+        <v>58547</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,14 +1944,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91349</v>
+        <v>91504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,14 +2045,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>58531</v>
+        <v>58575</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,14 +2146,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91349</v>
+        <v>91504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,14 +2247,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91707</v>
+        <v>91862</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,14 +2348,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98384</v>
+        <v>98549</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,14 +2449,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57729</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,14 +2563,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91314</v>
+        <v>91469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,14 +2664,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91707</v>
+        <v>91862</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,14 +2765,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91707</v>
+        <v>91862</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,14 +2866,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91314</v>
+        <v>91469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,14 +2967,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91721</v>
+        <v>91876</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,14 +3077,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>57669</v>
+        <v>57713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,7 +3186,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3247,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91349</v>
+        <v>91504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3337,14 +3393,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91367</v>
+        <v>91522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3434,14 +3494,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91349</v>
+        <v>91504</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,14 +3595,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>127127715</v>
       </c>
       <c r="B30" t="n">
-        <v>57669</v>
+        <v>57713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3636,14 +3704,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91645</v>
+        <v>91800</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3733,14 +3805,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>58503</v>
+        <v>58547</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3831,14 +3907,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3933,14 +4013,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>57729</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4043,14 +4127,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91349</v>
+        <v>91504</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,7 +4228,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>58547</v>
+        <v>58551</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>58575</v>
+        <v>58579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>57729</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91876</v>
+        <v>91880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>127127715</v>
       </c>
       <c r="B30" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>58547</v>
+        <v>58551</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57729</v>
+        <v>57733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>58551</v>
+        <v>58554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>58579</v>
+        <v>58582</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91880</v>
+        <v>91885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>127127715</v>
       </c>
       <c r="B30" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>58551</v>
+        <v>58554</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91893</v>
+        <v>91896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91896</v>
+        <v>91899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>58554</v>
+        <v>58556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>58582</v>
+        <v>58584</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91899</v>
+        <v>91906</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>127127715</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>58554</v>
+        <v>58556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91906</v>
+        <v>91913</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>127127713</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>127127722</v>
       </c>
       <c r="B13" t="n">
-        <v>58556</v>
+        <v>58558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127127702</v>
       </c>
       <c r="B15" t="n">
-        <v>58584</v>
+        <v>58586</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>127127724</v>
       </c>
       <c r="B19" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91913</v>
+        <v>91915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>127127716</v>
       </c>
       <c r="B25" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>127127715</v>
       </c>
       <c r="B30" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>127127721</v>
       </c>
       <c r="B32" t="n">
-        <v>58556</v>
+        <v>58558</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>127127712</v>
       </c>
       <c r="B33" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127127723</v>
       </c>
       <c r="B34" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98595</v>
+        <v>98621</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91915</v>
+        <v>91924</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98621</v>
+        <v>98622</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91924</v>
+        <v>91925</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,14 +3421,10 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3715,7 +3711,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98623</v>
+        <v>98627</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91925</v>
+        <v>91928</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98627</v>
+        <v>98629</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91928</v>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2024 artfynd.xlsx
+++ b/artfynd/A 58854-2024 artfynd.xlsx
@@ -1955,7 +1955,7 @@
         <v>127127709</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>127127707</v>
       </c>
       <c r="B16" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127127704</v>
       </c>
       <c r="B17" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127127727</v>
       </c>
       <c r="B18" t="n">
-        <v>98629</v>
+        <v>98633</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>127127700</v>
       </c>
       <c r="B20" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>127127705</v>
       </c>
       <c r="B21" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127127703</v>
       </c>
       <c r="B22" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127127701</v>
       </c>
       <c r="B23" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>127127725</v>
       </c>
       <c r="B24" t="n">
-        <v>91930</v>
+        <v>91934</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>127127710</v>
       </c>
       <c r="B27" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>127127726</v>
       </c>
       <c r="B28" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>127127711</v>
       </c>
       <c r="B29" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>127127718</v>
       </c>
       <c r="B31" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>127127708</v>
       </c>
       <c r="B35" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
